--- a/Nhom01/SE_9/SE_9_Nhom01_ProductBacklog.xlsx
+++ b/Nhom01/SE_9/SE_9_Nhom01_ProductBacklog.xlsx
@@ -522,7 +522,7 @@
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>Acceptance criteria theo rubric môn học</t>
+          <t>Tiêu chí nghiệm thu theo yêu cầu môn học</t>
         </is>
       </c>
       <c r="C5" s="8" t="inlineStr">
@@ -559,7 +559,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>Rows are User Stories ordered by PO; each has ID, short description, MoSCoW priority, proposed sprint and status.</t>
+          <t>Các mục trong danh sách công việc là các câu chuyện người dùng, được Chủ sản phẩm sắp thứ tự; mỗi mục có mã, mô tả ngắn, mức ưu tiên theo bốn mức, đợt phát triển dự kiến và trạng thái.</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
@@ -574,7 +574,7 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>Product Backlog rows 2–27, columns A:I; UserStory rows 2–17. PBI titles correspond broadly to Feature titles; the files contain different ID sets (26 PBI vs 16 US). Owner is column H.</t>
+          <t>PBI-001–PBI-026; US-001–US-016</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
@@ -596,7 +596,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>MoSCoW has the slide meanings: Must required for v1.0, Should, Could optional, Won’t out of release.</t>
+          <t>Bốn mức ưu tiên được dùng đúng nghĩa: Bắt buộc là bắt buộc cho phiên bản 1.0; Nên có là nên có; Có thể có là tùy chọn; Không đưa vào là không nằm trong đợt phát hành này.</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
@@ -611,7 +611,7 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>Column F, rows 2–27</t>
+          <t>PBI-001–PBI-026</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>The fuller backlog item has business value, estimate, owner and link to acceptance criteria.</t>
+          <t>Mục công việc đầy đủ còn có giá trị nghiệp vụ, ước lượng, người phụ trách và liên kết tới tiêu chí nghiệm thu.</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -648,7 +648,7 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>Columns D:H, rows 2–27</t>
+          <t>PBI-001–PBI-026; AC-EP001-01–AC-EP005-05</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
